--- a/artfynd/A 10518-2026 artfynd.xlsx
+++ b/artfynd/A 10518-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94108702</v>
+        <v>94109204</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583295.9166590996</v>
+        <v>583124</v>
       </c>
       <c r="R2" t="n">
-        <v>6741680.215489378</v>
+        <v>6741555</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,65 +783,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94109131</v>
+        <v>94109445</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583151.0503432212</v>
+        <v>583221</v>
       </c>
       <c r="R3" t="n">
-        <v>6741537.677721059</v>
+        <v>6741645</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94109445</v>
+        <v>94108615</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,35 +902,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn 4847, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583221.4383866655</v>
+        <v>583315</v>
       </c>
       <c r="R4" t="n">
-        <v>6741644.299443689</v>
+        <v>6741717</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -991,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +972,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rynkskinn på grov förrötad granlåga ca 10 m öster om kolarkoja.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,57 +1004,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94108666</v>
+        <v>94108702</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583308.2845279681</v>
+        <v>583296</v>
       </c>
       <c r="R5" t="n">
-        <v>6741674.156387975</v>
+        <v>6741681</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,51 +1112,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94108615</v>
+        <v>94109465</v>
       </c>
       <c r="B6" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ivantjärn 4847, Ockelbo, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583314.6372731245</v>
+        <v>583212</v>
       </c>
       <c r="R6" t="n">
-        <v>6741716.296291469</v>
+        <v>6741688</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rynkskinn på grov förrötad granlåga ca 10 m öster om kolarkoja.</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,15 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94109204</v>
+        <v>97604825</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,35 +1231,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn, V Mursveden, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583123.7679865821</v>
+        <v>583204</v>
       </c>
       <c r="R7" t="n">
-        <v>6741554.132890374</v>
+        <v>6741681</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1336,22 +1285,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,64 +1305,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94109438</v>
+        <v>97604826</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn, V Mursveden, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583212.4009966104</v>
+        <v>583167</v>
       </c>
       <c r="R8" t="n">
-        <v>6741675.338736652</v>
+        <v>6741554</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,22 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,27 +1406,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94109259</v>
+        <v>94108689</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,49 +1433,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583108.9555497216</v>
+        <v>583284</v>
       </c>
       <c r="R9" t="n">
-        <v>6741539.139312183</v>
+        <v>6741685</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1582,7 +1493,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1503,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,51 +1530,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94109465</v>
+        <v>94108666</v>
       </c>
       <c r="B10" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583212.1053294018</v>
+        <v>583308</v>
       </c>
       <c r="R10" t="n">
-        <v>6741688.027038684</v>
+        <v>6741675</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1695,7 +1607,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1617,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,51 +1644,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94108689</v>
+        <v>94109131</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583283.0828024009</v>
+        <v>583151</v>
       </c>
       <c r="R11" t="n">
-        <v>6741685.287200025</v>
+        <v>6741537</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,50 +1766,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97604825</v>
+        <v>94109259</v>
       </c>
       <c r="B12" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ivantjärn, V Mursveden, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583203.9550299596</v>
+        <v>583108</v>
       </c>
       <c r="R12" t="n">
-        <v>6741681.001260362</v>
+        <v>6741539</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,22 +1846,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,31 +1876,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
-        </is>
-      </c>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97604695</v>
+        <v>94109438</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,16 +1917,18 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ivantjärn, V Mursveden, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583264.464112937</v>
+        <v>583212</v>
       </c>
       <c r="R13" t="n">
-        <v>6741644.814118322</v>
+        <v>6741675</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2031,22 +1955,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,53 +1985,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
-        </is>
-      </c>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97604826</v>
+        <v>97604689</v>
       </c>
       <c r="B14" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2117,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583166.8175079527</v>
+        <v>583095</v>
       </c>
       <c r="R14" t="n">
-        <v>6741553.67031049</v>
+        <v>6741615</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2147,22 +2062,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2193,15 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97604696</v>
+        <v>97604695</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583270.0446825577</v>
+        <v>583265</v>
       </c>
       <c r="R15" t="n">
-        <v>6741678.147267408</v>
+        <v>6741645</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2266,19 +2166,9 @@
           <t>2021-09-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,6 +2196,305 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>97604696</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ivantjärn, V Mursveden, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>583270</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6741678</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>97604833</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ivantjärn, V Mursveden, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>583117</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6741635</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-05-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-05-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129590996</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vid Jädraån, Ivantjärn, Gstr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>583116</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6741651</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
